--- a/Game/Obj.xlsx
+++ b/Game/Obj.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="586">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252 Patch 2</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">momiji</t>
@@ -1253,6 +1253,15 @@
     <t xml:space="preserve">竜骨</t>
   </si>
   <si>
+    <t xml:space="preserve">144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stepping stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">踏み石</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -1373,6 +1382,9 @@
     <t xml:space="preserve">EA 23.247 Patch 1</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.287 Patch 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lá phong đỏ</t>
   </si>
   <si>
@@ -1758,6 +1770,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gò xương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đá lát bước</t>
   </si>
 </sst>
 </file>
@@ -1863,10 +1878,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1882,10 +1897,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1901,10 +1916,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -1920,10 +1935,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C6" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -1939,10 +1954,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1958,10 +1973,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -1977,10 +1992,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1996,10 +2011,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C10" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -2015,10 +2030,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2034,10 +2049,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2053,10 +2068,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2072,10 +2087,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C14" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2091,10 +2106,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2110,10 +2125,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2129,10 +2144,10 @@
         <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C17" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
@@ -2148,10 +2163,10 @@
         <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D18" t="s">
         <v>44</v>
@@ -2167,10 +2182,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C19" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
@@ -2186,10 +2201,10 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C20" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
@@ -2205,10 +2220,10 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C21" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -2224,10 +2239,10 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C22" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D22" t="s">
         <v>64</v>
@@ -2243,10 +2258,10 @@
         <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C23" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D23" t="s">
         <v>67</v>
@@ -2262,10 +2277,10 @@
         <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C24" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D24" t="s">
         <v>70</v>
@@ -2281,10 +2296,10 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C25" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D25" t="s">
         <v>73</v>
@@ -2300,10 +2315,10 @@
         <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C26" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D26" t="s">
         <v>76</v>
@@ -2319,10 +2334,10 @@
         <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D27" t="s">
         <v>79</v>
@@ -2338,10 +2353,10 @@
         <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C28" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D28" t="s">
         <v>82</v>
@@ -2357,10 +2372,10 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C29" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D29" t="s">
         <v>85</v>
@@ -2376,10 +2391,10 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C30" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D30" t="s">
         <v>88</v>
@@ -2395,10 +2410,10 @@
         <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C31" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D31" t="s">
         <v>91</v>
@@ -2414,10 +2429,10 @@
         <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C32" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -2433,10 +2448,10 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C33" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D33" t="s">
         <v>97</v>
@@ -2452,10 +2467,10 @@
         <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C34" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D34" t="s">
         <v>100</v>
@@ -2471,10 +2486,10 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C35" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D35" t="s">
         <v>103</v>
@@ -2490,10 +2505,10 @@
         <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C36" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D36" t="s">
         <v>106</v>
@@ -2509,10 +2524,10 @@
         <v>108</v>
       </c>
       <c r="B37" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C37" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -2528,10 +2543,10 @@
         <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C38" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D38" t="s">
         <v>112</v>
@@ -2547,10 +2562,10 @@
         <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C39" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D39" t="s">
         <v>115</v>
@@ -2566,10 +2581,10 @@
         <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C40" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D40" t="s">
         <v>118</v>
@@ -2585,10 +2600,10 @@
         <v>120</v>
       </c>
       <c r="B41" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C41" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D41" t="s">
         <v>121</v>
@@ -2604,10 +2619,10 @@
         <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C42" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D42" t="s">
         <v>124</v>
@@ -2623,10 +2638,10 @@
         <v>126</v>
       </c>
       <c r="B43" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C43" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D43" t="s">
         <v>127</v>
@@ -2642,10 +2657,10 @@
         <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C44" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D44" t="s">
         <v>130</v>
@@ -2661,10 +2676,10 @@
         <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C45" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D45" t="s">
         <v>133</v>
@@ -2680,10 +2695,10 @@
         <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C46" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D46" t="s">
         <v>82</v>
@@ -2699,10 +2714,10 @@
         <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D47" t="s">
         <v>138</v>
@@ -2718,10 +2733,10 @@
         <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C48" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D48" t="s">
         <v>141</v>
@@ -2737,10 +2752,10 @@
         <v>143</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C49" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -2756,10 +2771,10 @@
         <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C50" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D50" t="s">
         <v>44</v>
@@ -2775,10 +2790,10 @@
         <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C51" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D51" t="s">
         <v>147</v>
@@ -2794,10 +2809,10 @@
         <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C52" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D52" t="s">
         <v>150</v>
@@ -2813,10 +2828,10 @@
         <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C53" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D53" t="s">
         <v>153</v>
@@ -2832,10 +2847,10 @@
         <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C54" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2851,10 +2866,10 @@
         <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C55" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D55" t="s">
         <v>159</v>
@@ -2870,10 +2885,10 @@
         <v>161</v>
       </c>
       <c r="B56" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C56" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D56" t="s">
         <v>162</v>
@@ -2889,10 +2904,10 @@
         <v>164</v>
       </c>
       <c r="B57" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C57" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D57" t="s">
         <v>165</v>
@@ -2908,10 +2923,10 @@
         <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C58" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D58" t="s">
         <v>168</v>
@@ -2927,10 +2942,10 @@
         <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C59" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D59" t="s">
         <v>171</v>
@@ -2946,10 +2961,10 @@
         <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C60" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D60" t="s">
         <v>174</v>
@@ -2965,10 +2980,10 @@
         <v>176</v>
       </c>
       <c r="B61" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C61" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D61" t="s">
         <v>177</v>
@@ -2984,10 +2999,10 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C62" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D62" t="s">
         <v>180</v>
@@ -3003,10 +3018,10 @@
         <v>182</v>
       </c>
       <c r="B63" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C63" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D63" t="s">
         <v>183</v>
@@ -3022,10 +3037,10 @@
         <v>185</v>
       </c>
       <c r="B64" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C64" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D64" t="s">
         <v>186</v>
@@ -3041,10 +3056,10 @@
         <v>188</v>
       </c>
       <c r="B65" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C65" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D65" t="s">
         <v>189</v>
@@ -3060,10 +3075,10 @@
         <v>191</v>
       </c>
       <c r="B66" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C66" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D66" t="s">
         <v>192</v>
@@ -3079,10 +3094,10 @@
         <v>194</v>
       </c>
       <c r="B67" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C67" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D67" t="s">
         <v>195</v>
@@ -3098,10 +3113,10 @@
         <v>197</v>
       </c>
       <c r="B68" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C68" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D68" t="s">
         <v>198</v>
@@ -3117,10 +3132,10 @@
         <v>200</v>
       </c>
       <c r="B69" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C69" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D69" t="s">
         <v>201</v>
@@ -3136,10 +3151,10 @@
         <v>203</v>
       </c>
       <c r="B70" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C70" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D70" t="s">
         <v>204</v>
@@ -3155,10 +3170,10 @@
         <v>206</v>
       </c>
       <c r="B71" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C71" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D71" t="s">
         <v>207</v>
@@ -3174,10 +3189,10 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C72" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D72" t="s">
         <v>210</v>
@@ -3193,10 +3208,10 @@
         <v>212</v>
       </c>
       <c r="B73" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C73" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D73" t="s">
         <v>213</v>
@@ -3212,10 +3227,10 @@
         <v>215</v>
       </c>
       <c r="B74" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C74" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D74" t="s">
         <v>216</v>
@@ -3231,10 +3246,10 @@
         <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D75" t="s">
         <v>219</v>
@@ -3250,10 +3265,10 @@
         <v>221</v>
       </c>
       <c r="B76" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C76" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D76" t="s">
         <v>222</v>
@@ -3269,10 +3284,10 @@
         <v>224</v>
       </c>
       <c r="B77" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C77" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D77" t="s">
         <v>225</v>
@@ -3288,10 +3303,10 @@
         <v>227</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C78" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D78" t="s">
         <v>228</v>
@@ -3307,10 +3322,10 @@
         <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C79" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D79" t="s">
         <v>231</v>
@@ -3326,10 +3341,10 @@
         <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C80" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D80" t="s">
         <v>234</v>
@@ -3345,10 +3360,10 @@
         <v>236</v>
       </c>
       <c r="B81" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C81" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D81" t="s">
         <v>237</v>
@@ -3364,10 +3379,10 @@
         <v>239</v>
       </c>
       <c r="B82" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C82" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D82" t="s">
         <v>240</v>
@@ -3383,10 +3398,10 @@
         <v>242</v>
       </c>
       <c r="B83" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C83" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D83" t="s">
         <v>243</v>
@@ -3402,10 +3417,10 @@
         <v>244</v>
       </c>
       <c r="B84" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C84" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D84" t="s">
         <v>245</v>
@@ -3421,10 +3436,10 @@
         <v>247</v>
       </c>
       <c r="B85" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C85" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D85" t="s">
         <v>248</v>
@@ -3440,10 +3455,10 @@
         <v>250</v>
       </c>
       <c r="B86" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C86" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D86" t="s">
         <v>109</v>
@@ -3459,10 +3474,10 @@
         <v>251</v>
       </c>
       <c r="B87" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C87" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D87" t="s">
         <v>252</v>
@@ -3478,10 +3493,10 @@
         <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C88" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D88" t="s">
         <v>109</v>
@@ -3497,10 +3512,10 @@
         <v>255</v>
       </c>
       <c r="B89" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C89" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D89" t="s">
         <v>109</v>
@@ -3516,10 +3531,10 @@
         <v>256</v>
       </c>
       <c r="B90" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C90" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D90" t="s">
         <v>109</v>
@@ -3535,10 +3550,10 @@
         <v>257</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C91" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D91" t="s">
         <v>258</v>
@@ -3554,10 +3569,10 @@
         <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C92" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D92" t="s">
         <v>261</v>
@@ -3573,10 +3588,10 @@
         <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C93" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D93" t="s">
         <v>264</v>
@@ -3592,10 +3607,10 @@
         <v>266</v>
       </c>
       <c r="B94" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C94" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D94" t="s">
         <v>267</v>
@@ -3611,10 +3626,10 @@
         <v>269</v>
       </c>
       <c r="B95" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D95" t="s">
         <v>270</v>
@@ -3630,10 +3645,10 @@
         <v>272</v>
       </c>
       <c r="B96" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D96" t="s">
         <v>273</v>
@@ -3649,10 +3664,10 @@
         <v>275</v>
       </c>
       <c r="B97" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C97" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D97" t="s">
         <v>276</v>
@@ -3668,10 +3683,10 @@
         <v>278</v>
       </c>
       <c r="B98" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C98" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D98" t="s">
         <v>279</v>
@@ -3687,10 +3702,10 @@
         <v>281</v>
       </c>
       <c r="B99" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C99" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D99" t="s">
         <v>279</v>
@@ -3706,10 +3721,10 @@
         <v>282</v>
       </c>
       <c r="B100" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C100" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D100" t="s">
         <v>100</v>
@@ -3725,10 +3740,10 @@
         <v>283</v>
       </c>
       <c r="B101" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C101" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D101" t="s">
         <v>100</v>
@@ -3744,10 +3759,10 @@
         <v>284</v>
       </c>
       <c r="B102" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C102" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D102" t="s">
         <v>285</v>
@@ -3763,10 +3778,10 @@
         <v>287</v>
       </c>
       <c r="B103" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C103" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D103" t="s">
         <v>288</v>
@@ -3782,10 +3797,10 @@
         <v>290</v>
       </c>
       <c r="B104" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C104" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D104" t="s">
         <v>79</v>
@@ -3801,10 +3816,10 @@
         <v>291</v>
       </c>
       <c r="B105" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C105" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D105" t="s">
         <v>292</v>
@@ -3820,10 +3835,10 @@
         <v>294</v>
       </c>
       <c r="B106" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C106" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D106" t="s">
         <v>295</v>
@@ -3839,10 +3854,10 @@
         <v>297</v>
       </c>
       <c r="B107" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C107" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D107" t="s">
         <v>298</v>
@@ -3858,10 +3873,10 @@
         <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C108" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D108" t="s">
         <v>301</v>
@@ -3877,10 +3892,10 @@
         <v>303</v>
       </c>
       <c r="B109" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C109" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D109" t="s">
         <v>79</v>
@@ -3896,10 +3911,10 @@
         <v>304</v>
       </c>
       <c r="B110" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C110" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D110" t="s">
         <v>305</v>
@@ -3915,10 +3930,10 @@
         <v>307</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C111" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3934,10 +3949,10 @@
         <v>310</v>
       </c>
       <c r="B112" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C112" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D112" t="s">
         <v>311</v>
@@ -3953,10 +3968,10 @@
         <v>313</v>
       </c>
       <c r="B113" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C113" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D113" t="s">
         <v>314</v>
@@ -3972,10 +3987,10 @@
         <v>316</v>
       </c>
       <c r="B114" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C114" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D114" t="s">
         <v>317</v>
@@ -3991,10 +4006,10 @@
         <v>319</v>
       </c>
       <c r="B115" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C115" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D115" t="s">
         <v>320</v>
@@ -4010,10 +4025,10 @@
         <v>322</v>
       </c>
       <c r="B116" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C116" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D116" t="s">
         <v>323</v>
@@ -4029,10 +4044,10 @@
         <v>325</v>
       </c>
       <c r="B117" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C117" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D117" t="s">
         <v>326</v>
@@ -4048,10 +4063,10 @@
         <v>328</v>
       </c>
       <c r="B118" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C118" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D118" t="s">
         <v>329</v>
@@ -4067,10 +4082,10 @@
         <v>331</v>
       </c>
       <c r="B119" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C119" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D119" t="s">
         <v>332</v>
@@ -4086,10 +4101,10 @@
         <v>334</v>
       </c>
       <c r="B120" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C120" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D120" t="s">
         <v>335</v>
@@ -4105,10 +4120,10 @@
         <v>337</v>
       </c>
       <c r="B121" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C121" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D121" t="s">
         <v>338</v>
@@ -4124,10 +4139,10 @@
         <v>340</v>
       </c>
       <c r="B122" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C122" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D122" t="s">
         <v>341</v>
@@ -4143,10 +4158,10 @@
         <v>343</v>
       </c>
       <c r="B123" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D123" t="s">
         <v>22</v>
@@ -4162,10 +4177,10 @@
         <v>344</v>
       </c>
       <c r="B124" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C124" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D124" t="s">
         <v>345</v>
@@ -4181,10 +4196,10 @@
         <v>347</v>
       </c>
       <c r="B125" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C125" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D125" t="s">
         <v>348</v>
@@ -4200,10 +4215,10 @@
         <v>350</v>
       </c>
       <c r="B126" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C126" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D126" t="s">
         <v>351</v>
@@ -4219,10 +4234,10 @@
         <v>353</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C127" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D127" t="s">
         <v>354</v>
@@ -4238,10 +4253,10 @@
         <v>356</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C128" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D128" t="s">
         <v>357</v>
@@ -4257,10 +4272,10 @@
         <v>359</v>
       </c>
       <c r="B129" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C129" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D129" t="s">
         <v>360</v>
@@ -4276,10 +4291,10 @@
         <v>362</v>
       </c>
       <c r="B130" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C130" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D130" t="s">
         <v>363</v>
@@ -4295,10 +4310,10 @@
         <v>365</v>
       </c>
       <c r="B131" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C131" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D131" t="s">
         <v>366</v>
@@ -4314,10 +4329,10 @@
         <v>368</v>
       </c>
       <c r="B132" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C132" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D132" t="s">
         <v>369</v>
@@ -4333,10 +4348,10 @@
         <v>371</v>
       </c>
       <c r="B133" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C133" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D133" t="s">
         <v>372</v>
@@ -4352,10 +4367,10 @@
         <v>374</v>
       </c>
       <c r="B134" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C134" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D134" t="s">
         <v>375</v>
@@ -4371,10 +4386,10 @@
         <v>377</v>
       </c>
       <c r="B135" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C135" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D135" t="s">
         <v>378</v>
@@ -4390,10 +4405,10 @@
         <v>380</v>
       </c>
       <c r="B136" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C136" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D136" t="s">
         <v>381</v>
@@ -4409,10 +4424,10 @@
         <v>383</v>
       </c>
       <c r="B137" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C137" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D137" t="s">
         <v>384</v>
@@ -4428,10 +4443,10 @@
         <v>386</v>
       </c>
       <c r="B138" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C138" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D138" t="s">
         <v>387</v>
@@ -4447,10 +4462,10 @@
         <v>389</v>
       </c>
       <c r="B139" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C139" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D139" t="s">
         <v>390</v>
@@ -4466,10 +4481,10 @@
         <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C140" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D140" t="s">
         <v>393</v>
@@ -4485,10 +4500,10 @@
         <v>395</v>
       </c>
       <c r="B141" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C141" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D141" t="s">
         <v>396</v>
@@ -4504,10 +4519,10 @@
         <v>398</v>
       </c>
       <c r="B142" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C142" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D142" t="s">
         <v>399</v>
@@ -4523,10 +4538,10 @@
         <v>401</v>
       </c>
       <c r="B143" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C143" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D143" t="s">
         <v>402</v>
@@ -4542,10 +4557,10 @@
         <v>404</v>
       </c>
       <c r="B144" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C144" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D144" t="s">
         <v>405</v>
@@ -4561,10 +4576,10 @@
         <v>407</v>
       </c>
       <c r="B145" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C145" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D145" t="s">
         <v>408</v>
@@ -4580,10 +4595,10 @@
         <v>410</v>
       </c>
       <c r="B146" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C146" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D146" t="s">
         <v>159</v>
@@ -4593,6 +4608,25 @@
       </c>
       <c r="G146"/>
       <c r="H146"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>412</v>
+      </c>
+      <c r="B147" t="s">
+        <v>455</v>
+      </c>
+      <c r="C147" t="s">
+        <v>585</v>
+      </c>
+      <c r="D147" t="s">
+        <v>413</v>
+      </c>
+      <c r="E147" t="s">
+        <v>414</v>
+      </c>
+      <c r="G147"/>
+      <c r="H147"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
